--- a/data_extactor/batch_10_fa/batch_0002_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0002_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ADP Enterprise HR | ADP Workforce Now | Adobe Acrobat | Adobe PageMaker | Autodesk AutoCAD | Autodesk Revit | Blackbaud The Raiser's Edge | Delphi Technology | نرم‌افزار ایمیل | FileMaker Pro | نرم‌افزار حسابداری وجوه | Google Docs | Google Drive | نرم‌افزار Google Workspace | GroupMe | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Maximo Asset Management | IBM Notes | نرم‌افزار IBM Power Systems | Intuit QuickBooks | MicroFocus GroupWise | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Windows XP | Microsoft Word | Oracle Hyperion | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | SAP Business Objects | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | Sage 300 Construction and Real Estate | Sage 50 Accounting | Sage MAS 200 ERP | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | نرم‌افزار پایگاه داده Teradata | نرم‌افزار مرورگر وب | نرم‌افزار Yardi</t>
+          <t>ADP Enterprise HR | ADP Workforce Now | Adobe Acrobat | Adobe PageMaker | Autodesk AutoCAD | Autodesk Revit | Blackbaud The Raiser's Edge | Delphi Technology | نرم‌افزار ایمیل | FileMaker Pro | نرم‌افزار حسابداری صندوق | Google Docs | Google Drive | نرم‌افزار Google Workspace | GroupMe | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Maximo Asset Management | IBM Notes | نرم‌افزار IBM Power Systems | Intuit QuickBooks | MicroFocus GroupWise | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Windows XP | Microsoft Word | Oracle Hyperion | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | SAP Business Objects | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | Sage 300 Construction and Real Estate | Sage 50 Accounting | Sage MAS 200 ERP | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Teradata Database | نرم‌افزار مرورگر وب | نرم‌افزار Yardi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخنرانی | درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | نوشتن | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مکانیک | ساختمان و ساخت‌وساز | اداری | روانشناسی | آموزش و پرورش | کامپیوتر و الکترونیک | ریاضیات | مهندسی و فناوری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مکانیک | ساختمان و ساخت‌وساز | اداری | روان‌شناسی | آموزش و پرورش | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | حساسیت به مسئله | نظم‌دهی اطلاعات | استدلال استقرایی | بیان نوشتاری | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید نزدیک | دید دور | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | بینایی دور | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | محیط داخلی، دارای کنترل محیطی | تناوب تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | نتایج کاری و خروجی‌های سایر کارکنان | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا صحیح بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | اهمیت تکرار وظایف مشابه | نزدیکی فیزیکی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | اهمیت تکرار وظایف یکسان | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران ساخت‌وساز | بازرسان ساخت‌وساز و ساختمان | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کمک‌کاران، کارگران و جابه‌جاکنندگان مواد | سرپرستان خط اول کارکنان خانه‌داری و نظافت | سرپرستان خط اول کارکنان محوطه‌سازی، خدمات چمن و نگهداری زمین | سرپرستان خط اول اپراتورهای ماشین‌آلات جابه‌جایی مواد و وسایل نقلیه | سرپرستان خط اول مکانیک‌ها، نصاب‌ها و تعمیرکاران | سرپرستان خط اول کارکنان تولید و عملیات | مدیران عمومی و عملیاتی | مهندسان صنایع | مدیران تولید صنعتی | کارگران نگهداری و تعمیرات، عمومی | تحلیلگران مدیریت | متخصصان مدیریت پروژه | مدیران املاک، مستغلات و انجمن‌های اجتماعی | مدیران امنیتی | مدیران نصب انرژی خورشیدی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>مدیران خدمات اداری | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارگران تولید و بهره‌برداری | مدیران عمومی و عملیات | مهندسان صنایع | مدیران تولید صنعتی | کارگران نگهداری و تعمیرات عمومی | تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | مدیران املاک، مستغلات و انجمن‌های اجتماعی | مدیران امنیتی | مدیران نصب انرژی خورشیدی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار سیستم هشدار | نرم‌افزار Amazon Web Services AWS | مجموعه اداری Corel WordPerfect | نرم‌افزار سیستم اطلاع‌رسانی اضطراری | Facebook | FieldSoft AIMSonScene | نرم‌افزار فایروال | نرم‌افزار گرافیکی | سیستم مدیریت منابع انسانی HRMS | نرم‌افزار سیستم فرماندهی حادثه ICS | نرم‌افزار ردیابی موجودی | نرم‌افزار مدیریت نگهداری | نرم‌افزار نقشه‌برداری | McAfee | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Word | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle PeopleSoft | نرم‌افزار حقوق و دستمزد | نرم‌افزار مدیریت دسترسی فیزیکی | پلتفرم به عنوان سرویس PaaS | نرم‌افزار SAP | Twitter | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
+          <t>نرم‌افزار سیستم هشدار | نرم‌افزار Amazon Web Services AWS | Corel WordPerfect Office Suite | نرم‌افزار سیستم اطلاع‌رسانی اضطراری | Facebook | FieldSoft AIMSonScene | نرم‌افزار فایروال | نرم‌افزار گرافیکی | سیستم مدیریت منابع انسانی HRMS | نرم‌افزار سیستم فرماندهی حادثه ICS | نرم‌افزار ردیابی موجودی | نرم‌افزار مدیریت تعمیر و نگهداری | نرم‌افزار نقشه‌برداری | McAfee | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Word | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle PeopleSoft | نرم‌افزار حقوق و دستمزد | نرم‌افزار مدیریت دسترسی فیزیکی | پلتفرم به عنوان سرویس PaaS | نرم‌افزار SAP | Twitter | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | سخنرانی | نوشتن | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | سخن گفتن | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | قانون و دولت | مدیریت و اداره | خدمات مشتری و شخصی | پرسنل و منابع انسانی | آموزش و پرورش | کامپیوتر و الکترونیک | مخابرات | روانشناسی | ارتباطات و رسانه</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | قانون و دولت | مدیریت و اداره | خدمات مشتری و شخصی | پرسنل و منابع انسانی | آموزش و پرورش | رایانه و الکترونیک | مخابرات | روان‌شناسی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شنیداری | درک نوشتاری | استدلال قیاسی | استدلال استقرایی | بیان نوشتاری | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | دید نزدیک | نظم‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | خلاقیت | دید دور | سرعت بستار | سرعت ادراکی | اشتراک زمانی</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | اصالت | بینایی دور | سرعت بستار | سرعت ادراکی | تقسیم توجه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | نتایج کاری و خروجی‌های سایر کارکنان | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | تناوب تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای نشستن</t>
+          <t>ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | برنامه‌ریزان تداوم کسب‌وکار | مدیران انطباق | مدیران کامپیوتر و سیستم‌های اطلاعاتی | تحلیلگران جرم‌شناسی دیجیتال | مدیران مدیریت بحران | مدیران تسهیلات | سرپرستان خط اول کارکنان امنیتی | افسران نظارت بر قمار و بازرسان قمار | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تحلیلگران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیلگران اطلاعاتی | مدیران پیشگیری از خسارت | تحلیلگران مدیریت | متخصصان بهداشت و ایمنی شغلی | تست‌کنندگان نفوذ | متخصصان پیشگیری از خسارت خرده‌فروشی | نگهبانان امنیتی | متخصصان مدیریت امنیت</t>
+          <t>مدیران خدمات اداری | برنامه‌ریزان تداوم کسب‌وکار | مدیران انطباق | مدیران کامپیوتر و سیستم‌های اطلاعاتی | تحلیل‌گران جرم‌شناسی دیجیتال | مدیران مدیریت بحران | مدیران تسهیلات | سرپرستان خط اول کارکنان امنیتی | ماموران نظارت بر قمار و بازرسان قمار | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیلگران اطلاعاتی | مدیران پیشگیری از زیان | تحلیل‌گران مدیریت | متخصصان بهداشت و ایمنی شغلی | کارشناسان آزمون نفوذ | متخصصان پیشگیری از خسارت خرده‌فروشی | نگهبانان امنیتی | متخصصان مدیریت امنیت</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ACT! Premium | Adobe Distiller | Adobe Flex | برنامه‌نویسی کاربردی تجاری پیشرفته ABAP | Alpha Four | نرم‌افزار Amazon Web Services AWS | Apache Cassandra | Apache HTTP Server | Apache Hadoop | Apache Maven | Apache Pig | Apache Solr | Apache Tomcat | Apple Final Cut Pro | Apple iMovie | Apple iWork Keynote | Apple iWork Numbers | Apple iWork Pages | Apple macOS | Atlassian JIRA | Backbone.js | نرم‌افزار صورت‌حساب | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Borland Paradox | C | C# | C++ | Canu | Cisco Systems WAN Manager | نرم‌افزار رایانش ابری Citrix | زبان تجاری رایج COBOL | مجموعه اداری Corel WordPerfect | سیستم کنترل اطلاعات مشتری CICS | Dartware InterMapper | Drupal | زبان نشانه‌گذاری ابرمتنی پویا DHTML | Eclipse IDE | Embarcadero Delphi | Enterprise JavaBeans | نرم‌افزار یکپارچه‌سازی برنامه‌های سازمانی EAI | زبان نشانه‌گذاری ابرمتنی توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار پروتکل انتقال فایل FTP | FileMaker Pro | نرم‌افزار فایروال | Google Analytics | نرم‌افزار میز کمک | Hewlett Packard HP-UX | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتنی HTML | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | IBM WebSphere | IBM iSeries Access | Infor ERP Baan | نرم‌افزار محیط توسعه یکپارچه IDE | JavaScript | K2 Business Process Automation | KornShell | LAMP Stack | Langlais Computer Consultants CalMan | Linux | نرم‌افزار شبکه محلی LAN | Mac HelpMate | سیستم‌های اطلاعات مدیریت MIS | McAfee | MicroStrategy | معماری میکروسرویس‌ها | Microsoft .NET Framework | Microsoft Access | Microsoft Active Server Pages ASP | نرم‌افزار Microsoft Azure | Microsoft Business Contact Manager | Microsoft Dynamics | Microsoft Dynamics AX | Microsoft Dynamics CRM | Microsoft Dynamics GP | Microsoft Dynamics NAV | Microsoft Entourage | Microsoft Excel | Microsoft Exchange | Microsoft FrontPage | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | سرویس‌های گزارش‌دهی Microsoft SQL Server SSRS | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Visual Basic | نسخه اسکریپت‌نویسی Microsoft Visual Basic VBScript | Microsoft Visual FoxPro | Microsoft Visual Studio | Microsoft Windows Server | Microsoft Word | نرم‌افزار زیرساخت شبکه بی‌سیم موبایل | MongoDB | MySQL | Nagios | NetSuite ERP | Netscape Navigator | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Objective C | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle Java | Oracle PL/SQL | Oracle PeopleSoft | Oracle Primavera Systems | Oracle Siebel Server Sync | Oracle Solaris | Oracle WebLogic Server | Oracle iPlanet Web Server | PHP | نرم‌افزار Pegasus | نرم‌افزار Perforce Helix | Performance Solutions Technology ManagePro | Perl | Pilgrim Quality Solutions SmartSolve | PostgreSQL | Progress OpenEdge ABL | Progress OpenEdge Application Server | نرم‌افزار Progress OpenEdge Fathom Replication | Progress Sonic ESB | Progress WebSpeed Workshop | Puppet | Python | QUALCOMM Eudora | Qlik Tech QlikView | Quest Erwin Data Modeler | R | Red Hat Enterprise Linux | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Samba | اسکریپت پوسته | نرم‌افزار به عنوان سرویس SaaS | SolarWinds | Splunk Enterprise | Spring Framework | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Symantec Veritas File System | Symantec Veritas Volume Manager | نرم‌افزار TKSoftware RCM | Tableau | نرم‌افزار مالیاتی | نرم‌افزار برنامه‌های Telnet | نرم‌افزار پایگاه داده Teradata | The MathWorks MATLAB | UNIX | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | Zephyr EXTRA! Terminal Emulation</t>
+          <t>ACT! Premium | Adobe Distiller | Adobe Flex | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Alpha Four | نرم‌افزار Amazon Web Services AWS | Apache Cassandra | Apache HTTP Server | Apache Hadoop | Apache Maven | Apache Pig | Apache Solr | Apache Tomcat | Apple Final Cut Pro | Apple iMovie | Apple iWork Keynote | Apple iWork Numbers | Apple iWork Pages | Apple macOS | Atlassian JIRA | Backbone.js | نرم‌افزار صدور صورتحساب | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Borland Paradox | C | C# | C++ | Canu | Cisco Systems WAN Manager | نرم‌افزار رایانش ابری Citrix | زبان مشترک تجاری COBOL | Corel WordPerfect Office Suite | سیستم کنترل اطلاعات مشتری CICS | Dartware InterMapper | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | Eclipse IDE | Embarcadero Delphi | Enterprise JavaBeans | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار پروتکل انتقال فایل FTP | FileMaker Pro | نرم‌افزار فایروال | Google Analytics | نرم‌افزار میز کمک | Hewlett Packard HP-UX | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | IBM WebSphere | IBM iSeries Access | Infor ERP Baan | نرم‌افزار محیط توسعه یکپارچه IDE | JavaScript | K2 Business Process Automation | KornShell | LAMP Stack | Langlais Computer Consultants CalMan | Linux | نرم‌افزار شبکه محلی LAN | Mac HelpMate | سیستم‌های اطلاعات مدیریت MIS | McAfee | MicroStrategy | معماری میکروسرویس‌ها | Microsoft .NET Framework | Microsoft Access | Microsoft Active Server Pages ASP | نرم‌افزار Microsoft Azure | Microsoft Business Contact Manager | Microsoft Dynamics | Microsoft Dynamics AX | Microsoft Dynamics CRM | Microsoft Dynamics GP | Microsoft Dynamics NAV | Microsoft Entourage | Microsoft Excel | Microsoft Exchange | Microsoft FrontPage | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual FoxPro | Microsoft Visual Studio | Microsoft Windows Server | Microsoft Word | نرم‌افزار زیرساخت شبکه بی‌سیم موبایل | MongoDB | MySQL | Nagios | NetSuite ERP | Netscape Navigator | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Objective C | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle Java | Oracle PL/SQL | Oracle PeopleSoft | Oracle Primavera Systems | Oracle Siebel Server Sync | Oracle Solaris | Oracle WebLogic Server | Oracle iPlanet Web Server | PHP | نرم‌افزار Pegasus | نرم‌افزار Perforce Helix | Performance Solutions Technology ManagePro | Perl | Pilgrim Quality Solutions SmartSolve | PostgreSQL | Progress OpenEdge ABL | Progress OpenEdge Application Server | نرم‌افزار Progress OpenEdge Fathom Replication | Progress Sonic ESB | Progress WebSpeed Workshop | Puppet | Python | QUALCOMM Eudora | Qlik Tech QlikView | Quest Erwin Data Modeler | R | Red Hat Enterprise Linux | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Samba | Shell script | نرم‌افزار به عنوان سرویس SaaS | SolarWinds | Splunk Enterprise | Spring Framework | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Symantec Veritas File System | Symantec Veritas Volume Manager | نرم‌افزار TKSoftware RCM | Tableau | نرم‌افزار مالیاتی | نرم‌افزار برنامه‌های Telnet | Teradata Database | The MathWorks MATLAB | UNIX | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | Zephyr EXTRA! Terminal Emulation</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخنرانی | نظارت | نوشتن | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره | مهندسی و فناوری | زبان انگلیسی | پرسنل و منابع انسانی | ریاضیات | آموزش و پرورش</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره | مهندسی و فناوری | زبان انگلیسی | پرسنل و منابع انسانی | ریاضیات | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | بیان نوشتاری | نظم‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | خلاقیت | توانایی عددی | تجسم | انعطاف‌پذیری بستار | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | توانایی عددی | تجسم | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | صرف زمان برای نشستن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نتایج کاری و خروجی‌های سایر کارکنان | مکالمات تلفنی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | تناوب تصمیم‌گیری | اهمیت تکرار وظایف مشابه | محیط داخلی، دارای کنترل محیطی | پیامد خطا | سطح رقابت | صرف زمان برای انجام حرکات تکراری</t>
+          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | مکالمات تلفنی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل شرایط محیطی | پیامد خطا | سطح رقابت | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تحلیلگران هوش تجاری | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | معلمان علوم کامپیوتر، پس از متوسطه | تحلیلگران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربر کامپیوتر | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | تحلیلگران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | تحلیلگران مدیریت | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیلگران و تست‌کنندگان تضمین کیفیت نرم‌افزار</t>
+          <t>تحلیلگران هوش تجاری | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | اساتید علوم رایانه، پس از متوسطه | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | تحلیل‌گران مدیریت | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ADP Workforce Now | ARES Corporation PRISM Project Estimator | نرم‌افزار حساب‌های دریافتنی | Adobe Acrobat | نرم‌افزار Alteryx | Blackbaud The Raiser's Edge | نرم‌افزار مدیریت اعتبار | نرم‌افزار پایگاه داده | Delphi Technology | FileMaker Pro | نرم‌افزار حسابداری وجوه | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | سیستم اطلاعات منابع انسانی HRIS | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | Intuit QuickBooks | LexisNexis | اتوماسیون بازاریابی Marketo | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Windows | Microsoft Word | Moody's KMV FAMAS | NetSuite ERP | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Qlik Tech QlikView | R | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Sage 50 Accounting | نرم‌افزار Salesforce | زبان پرس‌وجوی ساختاریافته SQL | Tableau | نرم‌افزار مدیریت مالیات بر دارایی | نرم‌افزار مالیاتی | نرم‌افزار پایگاه داده Teradata | نرم‌افزار Workday | نرم‌افزار Yardi</t>
+          <t>ADP Workforce Now | ARES Corporation PRISM Project Estimator | نرم‌افزار حساب‌های دریافتنی | Adobe Acrobat | نرم‌افزار Alteryx | Blackbaud The Raiser's Edge | نرم‌افزار مدیریت اعتبار | نرم‌افزار پایگاه داده | Delphi Technology | FileMaker Pro | نرم‌افزار حسابداری صندوق | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | سیستم اطلاعات منابع انسانی (HRIS) | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | Intuit QuickBooks | LexisNexis | Marketo Marketing Automation | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Windows | Microsoft Word | Moody's KMV FAMAS | NetSuite ERP | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Qlik Tech QlikView | R | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Sage 50 Accounting | نرم‌افزار Salesforce | زبان پرس‌وجوی ساختاریافته SQL | Tableau | نرم‌افزار مدیریت مالیات بر دارایی | نرم‌افزار مالیاتی | Teradata Database | نرم‌افزار Workday | نرم‌افزار Yardi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخنرانی | گوش دادن فعال | درک مطلب | نوشتن | نظارت | ریاضیات | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | مدیریت و اداره | اقتصاد و حسابداری | ریاضیات | اداری | قانون و دولت | پرسنل و منابع انسانی | فروش و بازاریابی | زبان انگلیسی | آموزش و پرورش | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | اقتصاد و حسابداری | ریاضیات | اداری | قانون و دولت | پرسنل و منابع انسانی | فروش و بازاریابی | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | وضوح گفتار | استدلال قیاسی | بیان نوشتاری | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | دید نزدیک | نظم‌دهی اطلاعات | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | سرعت بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | سرعت بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | فشار زمانی | نتایج کاری و خروجی‌های سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | اهمیت تکرار وظایف مشابه | تناوب تصمیم‌گیری | تماس با دیگران | آزادی در تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | مکالمات تلفنی | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | فراوانی تصمیم‌گیری | ارتباط با دیگران | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مدیران خدمات اداری | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | تحلیلگران بودجه | تحلیلگران اعتبار | مجازکنندگان اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | بازرسان مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | سرپرستان خط اول کارکنان اداری و پشتیبانی دفتری | مدیران صندوق سرمایه‌گذاری | افسران وام | تحلیلگران مدیریت | کارمندان حساب‌های جدید | مشاوران مالی شخصی | نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | تحویل‌داران | خزانه‌داران و کنترل‌کنندگان</t>
+          <t>حسابداران و حسابرسان | مدیران خدمات اداری | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | تحلیلگران بودجه | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | بازرسان مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | مدیران صندوق سرمایه‌گذاری | مسئولان وام | تحلیل‌گران مدیریت | کارمندان حساب‌های جدید | مشاوران مالی شخصی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | تحویل‌داران | خزانه‌داران و کنترل‌کنندگان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADERANT Expert Back Office, Powered by Keystone | ADP Workforce Now | نرم‌افزار ADP | پردازش خودکار داده‌ها PC payroll for windows PCPW | Blackbaud The Raiser's Edge | Corel QuattroPro | نرم‌افزار خدمات حرفه‌ای Deltek | Exact Software Macola ES | FileMaker Pro | نرم‌افزار حسابداری وجوه | Hyperion Enterprise | Hyperion Solutions System 9 Planning | زبان نشانه‌گذاری ابرمتنی HTML | IBM Cognos Impromptu | IBM Lotus 1-2-3 | Infor ERP SyteLine | Intuit QuickBooks | نرم‌افزار هزینه‌یابی کار | MYOB Premier Accounting Small Business Suite | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Dynamics SL | Microsoft Excel | Microsoft FRx | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint Server | Microsoft Word | NetSuite ERP | Oracle Business Intelligence Enterprise Edition | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle Hyperion Planning | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | Sage 50 Accounting | Sage Fixed Asset Solution FAS | Sage MIP Fund Accounting | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار مالیاتی | نرم‌افزار Yardi</t>
+          <t>ADERANT Expert Back Office, Powered by Keystone | ADP Workforce Now | نرم‌افزار ADP | پردازش خودکار داده‌ها PC payroll for windows PCPW | Blackbaud The Raiser's Edge | Corel QuattroPro | نرم‌افزار خدمات حرفه‌ای Deltek | Exact Software Macola ES | FileMaker Pro | نرم‌افزار حسابداری صندوق | Hyperion Enterprise | Hyperion Solutions System 9 Planning | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Lotus 1-2-3 | Infor ERP SyteLine | Intuit QuickBooks | نرم‌افزار هزینه‌یابی کار | MYOB Premier Accounting Small Business Suite | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Dynamics SL | Microsoft Excel | Microsoft FRx | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint Server | Microsoft Word | NetSuite ERP | Oracle Business Intelligence Enterprise Edition | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle Hyperion Planning | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | Sage 50 Accounting | Sage Fixed Asset Solution FAS | Sage MIP Fund Accounting | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار مالیاتی | نرم‌افزار Yardi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخنرانی | گوش دادن فعال | نظارت | ریاضیات | یادگیری فعال | نوشتن | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک نوشتاری | دید نزدیک | درک شنیداری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | نظم‌دهی اطلاعات | استدلال ریاضی | توانایی عددی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>استدلال استقرایی | درک کتبی | بینایی نزدیک | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال ریاضی | توانایی عددی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نتایج کاری و خروجی‌های سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | اهمیت تکرار وظایف مشابه | سطح رقابت</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | سطح رقابت</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مدیران خدمات اداری | کارمندان دفترداری، حسابداری و حسابرسی | تحلیلگران بودجه | مدیران ارشد اجرایی | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | منشی‌های اجرایی و دستیاران اداری اجرایی | بازرسان مالی | مدیران مالی | تحلیلگران مالی و سرمایه‌گذاری | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان اداری و پشتیبانی دفتری | مدیران عمومی و عملیاتی | مدیران صندوق سرمایه‌گذاری | تحلیلگران مدیریت | کارمندان حقوق و دستمزد و زمان‌سنجی | مشاوران مالی شخصی | متخصصان مدیریت پروژه</t>
+          <t>حسابداران و حسابرسان | مدیران خدمات اداری | کارمندان دفترداری، حسابداری و حسابرسی | تحلیلگران بودجه | مدیران ارشد اجرایی | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | منشی‌های اجرایی و دستیاران اداری اجرایی | بازرسان مالی | مدیران مالی | تحلیلگران مالی و سرمایه‌گذاری | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | مدیران عمومی و عملیات | مدیران صندوق سرمایه‌گذاری | تحلیل‌گران مدیریت | کارمندان حقوق و دستمزد و ثبت زمان | مشاوران مالی شخصی | متخصصان مدیریت پروژه</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخنرانی | یادگیری فعال | نوشتن | نظارت | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره | قانون و دولت | کامپیوتر و الکترونیک | فروش و بازاریابی</t>
+          <t>اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره | قانون و دولت | رایانه و الکترونیک | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال استقرایی | نظم‌دهی اطلاعات | استدلال ریاضی | حساسیت به مسئله | وضوح گفتار | بیان نوشتاری | توانایی عددی | دید نزدیک | تشخیص گفتار | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | خلاقیت | روانی ایده‌ها | توجه انتخابی | سرعت ادراکی</t>
+          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی | حساسیت به مسئله | وضوح گفتار | بیان کتبی | توانایی عددی | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | صرف زمان برای نشستن | محیط داخلی، دارای کنترل محیطی | سطح رقابت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تناوب تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | تماس با دیگران | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | نتایج کاری و خروجی‌های سایر کارکنان</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | سطح رقابت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | ارتباط با دیگران | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | اکچوئرها | کارمندان کارگزاری | تحلیلگران بودجه | تحلیلگران هوش تجاری | مدیران ارشد اجرایی | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | اقتصاددانان | بازرسان مالی | مدیران مالی | تحلیلگران کمی مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | افسران وام | تحلیلگران مدیریت | تحلیلگران بازار و متخصصان بازاریابی | مشاوران مالی شخصی | نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | خزانه‌داران و کنترل‌کنندگان</t>
+          <t>حسابداران و حسابرسان | کارشناسان آمار بیمه (اکچوئری) | کارمندان کارگزاری | تحلیلگران بودجه | تحلیلگران هوش تجاری | مدیران ارشد اجرایی | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | اقتصاددانان | بازرسان مالی | مدیران مالی | تحلیلگران کمی مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | مسئولان وام | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مشاوران مالی شخصی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | خزانه‌داران و کنترل‌کنندگان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ABB Optimize IT Predict &amp; Control | AVEVA InTouch HMI | Adobe Acrobat | Adobe After Effects | Adobe InDesign | Adobe Photoshop | Apple Final Cut Pro | Autodesk AutoCAD | Citect IIM | CitectSCADA Reports | Clockware | نرم‌افزار تولید یکپارچه کامپیوتری CIM | نرم‌افزار زمان‌سنج تولید یکپارچه کامپیوتری CIM | نرم‌افزار مدیریت حمل‌ونقل انبار تولید یکپارچه کامپیوتری CIM | سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار پایگاه داده | سیستم کنترل توزیع‌شده DCS | Eko | نرم‌افزار ایمیل | سیستم مدیریت عملکرد کارکنان | نرم‌افزار زمان‌بندی کارکنان | Exact Software JobBOSS | FileMaker Pro | نرم‌افزار برنامه‌ریزی مالی | IBM Notes | IBM Rational ClearQuest | نرم‌افزار مدیریت تولید صنعتی و کنترل موجودی | Intuit QuickBooks | JamBoard | نرم‌افزار تحلیل گاز محل دفن زباله | Landtec System Software LFG Pro | سیستم تولید Marel MPS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Minitab | NetSuite ERP | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | PTC Creo Parametric | نرم‌افزار مدیریت کارخانه | ProcessPro Premier | نرم‌افزار معماری یکپارچه پلتفرم باز Prosys | نرم‌افزار راهکار مدیریت کیفیت QUMAS | Qlik Tech QlikView | SAP Business Objects | نرم‌افزار SAP | Scadex Technologies MAESTRO | Schneider Electric CitectSCADA | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | نرم‌افزار مرورگر وب | WorkSchedule.net | WorkTech MAXIMO | YouTube</t>
+          <t>ABB Optimize IT Predict &amp; Control | AVEVA InTouch HMI | Adobe Acrobat | Adobe After Effects | Adobe InDesign | Adobe Photoshop | Apple Final Cut Pro | Autodesk AutoCAD | Citect IIM | CitectSCADA Reports | Clockware | نرم‌افزار تولید یکپارچه کامپیوتری CIM | نرم‌افزار زمان‌سنج تولید یکپارچه کامپیوتری CIM | نرم‌افزار مدیریت حمل‌ونقل انبار تولید یکپارچه کامپیوتری CIM | سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار پایگاه داده | سیستم کنترل توزیع‌شده DCS | Eko | نرم‌افزار ایمیل | سیستم مدیریت عملکرد کارکنان | نرم‌افزار زمان‌بندی کارکنان | Exact Software JobBOSS | FileMaker Pro | نرم‌افزار برنامه‌ریزی مالی | IBM Notes | IBM Rational ClearQuest | نرم‌افزار مدیریت تولید صنعتی و کنترل موجودی | Intuit QuickBooks | JamBoard | نرم‌افزار تحلیل گاز محل دفن زباله | Landtec System Software LFG Pro | سیستم تولید Marel MPS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Minitab | NetSuite ERP | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | PTC Creo Parametric | نرم‌افزار مدیریت کارخانه | ProcessPro Premier | نرم‌افزار معماری یکپارچه پلتفرم باز Prosys | نرم‌افزار راهکار مدیریت کیفیت QUMAS | Qlik Tech QlikView | SAP Business Objects | نرم‌افزار SAP | Scadex Technologies MAESTRO | Schneider Electric CitectSCADA | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار مرورگر وب | WorkSchedule.net | WorkTech MAXIMO | YouTube</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخنرانی | درک مطلب | گوش دادن فعال | استراتژی‌های یادگیری | یادگیری فعال | نوشتن | ریاضیات</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و پردازش | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | ریاضیات | پرسنل و منابع انسانی | زبان انگلیسی | مکانیک | مهندسی و فناوری</t>
+          <t>تولید و فرآوری | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | ریاضیات | پرسنل و منابع انسانی | زبان انگلیسی | مکانیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | نظم‌دهی اطلاعات | درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | بیان نوشتاری | دید نزدیک | انعطاف‌پذیری دسته‌بندی | تجسم | سرعت ادراکی | توانایی عددی | استدلال ریاضی | خلاقیت | دید دور | توجه انتخابی | انعطاف‌پذیری بستار</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | بیان کتبی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | تجسم | سرعت ادراکی | توانایی عددی | استدلال ریاضی | اصالت | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش‌های ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | نتایج کاری و خروجی‌های سایر کارکنان | اهمیت دقیق یا صحیح بودن | تناوب تصمیم‌گیری | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل محیطی نیست | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | پیامدهای کاری و نتایج سایر کارکنان | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران تولید سوخت‌های زیستی | مدیران نیروگاه زیست‌توده | مدیران ساخت‌وساز | سرپرستان خط اول کمک‌کاران، کارگران و جابه‌جاکنندگان مواد | سرپرستان خط اول مکانیک‌ها، نصاب‌ها و تعمیرکاران | سرپرستان خط اول کارکنان تولید و عملیات | مدیران عمومی و عملیاتی | مدیران تولید زمین‌گرمایی | مدیران تولید برق‌آبی | تکنسین‌ها و فناوران مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک | مهندسان تولید | مهندسان مکانیک | کارمندان تولید، برنامه‌ریزی و اعزام | متخصصان مدیریت پروژه | مدیران سیستم‌های کنترل کیفیت | مدیران زنجیره تأمین | تیم مونتاژکاران | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>مدیران تولید سوخت‌های زیستی | مدیران نیروگاه‌های زیست‌توده | مدیران ساخت‌وساز | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارگران تولید و بهره‌برداری | مدیران عمومی و عملیات | مدیران تولید زمین‌گرمایی | مدیران تولید برق‌آبی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک | مهندسان تولید | مهندسان مکانیک | کارمندان تولید، برنامه‌ریزی و هماهنگی | متخصصان مدیریت پروژه | مدیران سیستم‌های کنترل کیفیت | مدیران زنجیره تأمین | مونتاژکاران تیمی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نوشتن | سخنرانی | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و پردازش | آموزش و پرورش | زبان انگلیسی | شیمی | خدمات مشتری و شخصی | مدیریت و اداره | ریاضیات | مهندسی و فناوری | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | پرسنل و منابع انسانی</t>
+          <t>تولید و فرآوری | آموزش و پرورش | زبان انگلیسی | شیمی | خدمات مشتری و شخصی | مدیریت و اداره | ریاضیات | مهندسی و فناوری | ایمنی و امنیت عمومی | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | نظم‌دهی اطلاعات | انعطاف‌پذیری بستار | دید دور | تشخیص گفتار | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | سرعت بستار | توانایی عددی | استدلال ریاضی | خلاقیت | تشخیص رنگ بصری</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی دور | تشخیص گفتار | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | سرعت بستار | توانایی عددی | استدلال ریاضی | اصالت | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تناوب تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | فشار زمانی | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | نتایج کاری و خروجی‌های سایر کارکنان | سطح رقابت | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای نشستن | موقعیت‌های تعارض | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه</t>
+          <t>ایمیل | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | فشار زمانی | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | سطح رقابت | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای نشستن | موقعیت‌های تعارض | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و فناوران کالیبراسیون | تکنسین‌های شیمی | شیمیدانان | مدیران انطباق | سرپرستان خط اول کارکنان تولید و عملیات | تکنسین‌های علوم غذایی | دانشمندان و فناوران مواد غذایی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌ها و فناوران مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | بازرسان، تست‌کنندگان، مرتب‌کنندگان، نمونه‌گیران و وزن‌کنندگان | مهندسان تولید | مهندسان مکانیک | مدیران علوم طبیعی | متخصصان مدیریت پروژه | تحلیلگران کنترل کیفیت | مدیران امور نظارتی | تحلیلگران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی</t>
+          <t>تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌های شیمی | شیمی‌دانان | مدیران انطباق | سرپرستان رده اول کارگران تولید و بهره‌برداری | تکنسین‌های علوم غذایی | دانشمندان و تکنولوژیست‌های علوم غذایی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | مهندسان تولید | مهندسان مکانیک | مدیران علوم طبیعی | متخصصان مدیریت پروژه | تحلیل‌گران کنترل کیفیت | مدیران امور نظارتی | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار ثبت داده | Infostat RIMBase | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار زمان‌بندی پرسنل</t>
+          <t>نرم‌افزار ثبت داده‌ها | Infostat RIMBase | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار زمان‌بندی پرسنل</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخنرانی | نظارت | گوش دادن فعال | نوشتن | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال | نگارش | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | مدیریت و اداره | تولید و پردازش | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | فیزیک | طراحی | شیمی | اداری | قانون و دولت | کامپیوتر و الکترونیک | ساختمان و ساخت‌وساز | اقتصاد و حسابداری</t>
+          <t>مکانیک | مدیریت و اداره | تولید و فرآوری | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | فیزیک | طراحی | شیمی | اداری | قانون و دولت | رایانه و الکترونیک | ساختمان و ساخت‌وساز | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | درک نوشتاری | بیان نوشتاری | وضوح گفتار | نظم‌دهی اطلاعات | دید نزدیک | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی | دید دور | روانی ایده‌ها | توجه انتخابی | تجسم | سرعت ادراکی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | درک کتبی | بیان کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی | بینایی دور | روانی ایده‌ها | توجه انتخابی | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | سلامت و ایمنی سایر کارکنان | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش‌های ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | نتایج کاری و خروجی‌های سایر کارکنان | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تماس با دیگران | محیط داخلی، دارای کنترل محیطی نیست | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | فشار زمانی | پیامد خطا | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | ارتباط با دیگران | محیط داخلی، بدون کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | فشار زمانی | پیامد خطا | فضای باز، در معرض تمام شرایط آب و هوایی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنسین‌های پردازش سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران فناوری و توسعه محصول سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه زیست‌توده | مهندسان انرژی، به جز باد و خورشید | اپراتورهای نیروگاه گاز | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مدیران تولید صنعتی | مهندسان نفت | اپراتورهای نیروگاه | مدیران سیستم‌های کنترل کیفیت | اپراتورهای نیروگاه و سیستم تصفیه آب و فاضلاب | مهندسان آب/فاضلاب | مدیران توسعه انرژی باد | مهندسان انرژی باد | مدیران عملیات انرژی باد | تکنسین‌های خدمات توربین بادی</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان انرژی، به جز باد و خورشید | اپراتورهای واحدهای گاز | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مدیران تولید صنعتی | مهندسان نفت | اپراتورهای نیروگاه برق | مدیران سیستم‌های کنترل کیفیت | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | مهندسان آب و فاضلاب | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | مدیران عملیات انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نظارت | سخنرانی | نوشتن | استراتژی‌های یادگیری | یادگیری فعال | علوم | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نظارت | سخن گفتن | نگارش | راهبردهای یادگیری | یادگیری فعال | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و پردازش | مدیریت و اداره | مکانیک | مهندسی و فناوری | شیمی | ریاضیات | کامپیوتر و الکترونیک | پرسنل و منابع انسانی | فیزیک | اداری | آموزش و پرورش | زبان انگلیسی | طراحی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | اقتصاد و حسابداری</t>
+          <t>تولید و فرآوری | مدیریت و اداره | مکانیک | مهندسی و فناوری | شیمی | ریاضیات | رایانه و الکترونیک | پرسنل و منابع انسانی | فیزیک | اداری | آموزش و پرورش | زبان انگلیسی | طراحی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | وضوح گفتار | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | دید نزدیک | توجه انتخابی | استدلال استقرایی | اشتراک زمانی | انعطاف‌پذیری بستار | سرعت ادراکی | دید دور | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | خلاقیت | روانی ایده‌ها | تشخیص رنگ بصری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | بینایی نزدیک | توجه انتخابی | استدلال استقرایی | تقسیم توجه | انعطاف‌پذیری بستار | سرعت ادراکی | بینایی دور | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | نتایج کاری و خروجی‌های سایر کارکنان | تماس با دیگران | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش‌های ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تناوب تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی نیست | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | فشار زمانی | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | پیامد خطا | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | سرعت تعیین‌شده توسط سرعت تجهیزات | اهمیت تکرار وظایف مشابه | فضای باز، زیر پوشش | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | پیامدهای کاری و نتایج سایر کارکنان | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضای باز، در معرض تمام شرایط آب و هوایی | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | سرعت تعیین‌شده توسط سرعت تجهیزات | اهمیت تکرار وظایف یکسان | فضای باز، زیر سقف | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های پردازش سوخت‌های زیستی | مدیران فناوری و توسعه محصول سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه زیست‌توده | مهندسان شیمی | اپراتورهای نیروگاه و سیستم شیمیایی | مهندسان انرژی، به جز باد و خورشید | اپراتورهای نیروگاه گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مهندسان صنایع | مدیران تولید صنعتی | مهندسان تولید | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و اندازه‌گیرها | اپراتورهای نیروگاه | مدیران سیستم‌های کنترل کیفیت | اپراتورهای نیروگاه و سیستم تصفیه آب و فاضلاب | مدیران توسعه انرژی باد | مدیران عملیات انرژی باد</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | اپراتورهای کارخانه و سامانه‌های شیمیایی | مهندسان انرژی، به جز باد و خورشید | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مهندسان صنایع | مدیران تولید صنعتی | مهندسان تولید | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای نیروگاه برق | مدیران سیستم‌های کنترل کیفیت | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | مدیران توسعه انرژی بادی | مدیران عملیات انرژی بادی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0002_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0002_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | ایمنی و امنیت عمومی | امور اداری و منابع انسانی | مکانیک | ساختمان و ساخت‌وساز | اداری | روان‌شناسی | آموزش و تدریس | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مکانیک | ساختمان و ساخت‌وساز | اداری | روان‌شناسی | آموزش و پرورش | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال استقرایی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید نزدیک | دید دور | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | بینایی دور | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران ساخت‌وساز | بازرسان ساختمان و سازه | سرپرستان رده‌اول مشاغل ساختمانی و کارگران استخراج | سرپرستان رده‌اول کمک‌کاران، کارگران ساده و جابه‌جاکنندگان دستی کالا | سرپرستان رده‌اول کارکنان خدمات و نظافت اماکن | سرپرستان رده‌اول کارکنان فضای سبز، باغبانی و محوطه‌سازی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیهٔ جابه‌جایی مواد | سرپرستان رده‌اول مکانیک‌ها، نصاب‌ها و تعمیرکاران | سرپرستان رده‌اول کارگران تولید و بهره‌برداری | مدیران عمومی و عملیاتی | مهندسان صنایع | مدیران تولید صنعتی | کارگران عمومی نگهداری و تعمیرات | تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | مدیران املاک، مستغلات و مجتمع‌های مسکونی | مدیران حراست و انتظامات | مدیران نصب تأسیسات انرژی خورشیدی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارگران تولید و عملیات | مدیران کل و مدیران عملیات | مهندسان صنایع | مدیران تولید صنعتی | کارگران عمومی تعمیرات و نگهداری تاسیسات | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان مدیریت پروژه | مدیران املاک، مستغلات و مجتمع‌های مسکونی | مدیران حراست و انتظامات | مدیران اجرای پروژه‌های انرژی خورشیدی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نظارت | سخن گفتن | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | سخن گفتن | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | حقوق و مقررات دولتی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | امور اداری و منابع انسانی | آموزش و تدریس | رایانه و الکترونیک | مخابرات | روان‌شناسی | ارتباطات و رسانه</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | قانون و دولت | مدیریت و اداره | خدمات مشتری و شخصی | پرسنل و منابع انسانی | آموزش و پرورش | رایانه و الکترونیک | مخابرات | روان‌شناسی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | روانی کلام و سیالی ایده‌ها | وضوح گفتار | تشخیص گفتار | دید نزدیک | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | درک روابط فضایی | نوآوری و اصالت | دید دور | تمایز دیداری اشکال پنهان | سرعت ادراک | تقسیم توجه</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | اصالت | بینایی دور | سرعت بستار | سرعت ادراکی | تقسیم توجه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارشناسان تداوم کسب‌وکار | مدیران انطباق و نظارت بر مقررات | مدیران رایانه و سیستم‌های اطلاعاتی | کارشناسان تحلیل جرم‌شناسی دیجیتال | مدیران مدیریت بحران | مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول مأموران حراست و نگهبانی | مأموران نظارت تصویری و بازرسان اماکن ویژه | مهندسان بهداشت و ایمنی حرفه‌ای، به‌جز مهندسان و بازرسان ایمنی معدن | کارشناسان امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران اطلاعاتی و امنیتی | مدیران پیشگیری از هدررفت منابع | تحلیل‌گران مدیریت | متخصصان بهداشت حرفه‌ای و ایمنی کار | کارشناسان آزمون نفوذپذیری | کارشناسان پیشگیری از سرقت و کسری کالا | نگهبانان و مأموران حفاظت | متخصصان مدیریت حراست و امنیت</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان برنامه‌ریزی تداوم کسب‌وکار | مدیران تطبیق و نظارت مقرراتی | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | مدیران مدیریت بحران و پدافند غیرعامل | مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول کارکنان حراست و انتظامات | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران داده‌ها و اطلاعات امنیتی | مدیران پیشگیری از اتلاف منابع و صیانت از دارایی‌ها | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان بهداشت حرفه‌ای و ایمنی کار | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | نگهبانان و ماموران حراست | کارشناسان مدیریت حراست و امنیت فیزیکی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | نظارت | نگارش | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | مهندسی و فناوری | زبان انگلیسی | امور اداری و منابع انسانی | ریاضیات | آموزش و تدریس</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره | مهندسی و فناوری | زبان انگلیسی | پرسنل و منابع انسانی | ریاضیات | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | بیان کتبی | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | روانی کلام و سیالی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | نوآوری و اصالت | مهارت محاسبات عددی | تجسم فضایی | درک روابط فضایی | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | توانایی عددی | تجسم | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری | معماران شبکه رایانه‌ای | کارشناسان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان رایانه | مدرسان علوم رایانه دانشگاه | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | کارشناسان پشتیبانی کاربران رایانه | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد و مدارک | کارشناسان امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه‌های فناوری اطلاعات | تحلیل‌گران مدیریت | راهبران شبکه و سیستم‌های رایانه‌ای | متخصصان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | کارشناسان آزمون و تضمین کیفیت نرم‌افزار</t>
+          <t>تحلیل‌گران هوش تجاری | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | استادان علوم رایانه، آموزش عالی | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه‌های فناوری اطلاعات | کارشناسان تحلیل مدیریت و روش‌ها | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | ریاضیات | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | اقتصاد و حسابداری | ریاضیات | اداری | حقوق و مقررات دولتی | امور اداری و منابع انسانی | فروش و بازاریابی | زبان انگلیسی | آموزش و تدریس | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | اقتصاد و حسابداری | ریاضیات | اداری | قانون و دولت | پرسنل و منابع انسانی | فروش و بازاریابی | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | دید نزدیک | مرتب‌سازی اطلاعات | مهارت محاسبات عددی | استدلال ریاضی | روانی کلام و سیالی ایده‌ها | درک روابط فضایی | انعطاف‌پذیری در طبقه‌بندی | تمایز دیداری اشکال پنهان</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | سرعت بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مدیران خدمات اداری | کارمندان امور دفتری، حسابداری و حسابرسی | کارمندان کارگزاری | تحلیل‌گران بودجه | تحلیل‌گران اعتباری | متصدیان بررسی، تأیید و ثبت اعتبارات | مشاوران اعتباری و مالی | ممیزان و بازرسان مالی | متخصصان مدیریت ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان پرداخت تسهیلات و اعتبارات | تحلیل‌گران مدیریت | متصدیان افتتاح حساب و خدمات مشتریان بانکی | مشاوران مالی فردی | کارگزاران و نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | تحویلداران بانک | خزانه‌داران و مدیران مالی</t>
+          <t>حسابداران و حسابرسان | مدیران خدمات اداری و پشتیبانی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | تحلیل‌گران بودجه | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | بازرسان و ارزیابان مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان و مسئولان تسهیلات و اعتبارات | کارشناسان تحلیل مدیریت و روش‌ها | متصدیان افتتاح حساب | مشاوران مالی فردی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | تحویل‌داران و متصدیان امور بانکی | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | زبان انگلیسی | مدیریت و امور اداری | ریاضیات | امور اداری و منابع انسانی</t>
+          <t>اقتصاد و حسابداری | زبان انگلیسی | مدیریت و اداره | ریاضیات | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک کتبی | دید نزدیک | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال ریاضی | مهارت محاسبات عددی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و سیالی ایده‌ها | نوآوری و اصالت | سرعت ادراک | درک روابط فضایی</t>
+          <t>استدلال استقرایی | درک کتبی | بینایی نزدیک | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال ریاضی | توانایی عددی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مدیران خدمات اداری | کارمندان امور دفتری، حسابداری و حسابرسی | تحلیل‌گران بودجه | مدیران ارشد اجرایی | مدیران حقوق، دستمزد و مزایا | کارشناسان تحلیل شغل، حقوق و مزایا | تحلیل‌گران اعتباری | مسئولان دفاتر و دستیاران اجرایی مدیریت | ممیزان و بازرسان مالی | مدیران امور مالی | تحلیل‌گران مالی و سرمایه‌گذاری | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران عمومی و عملیاتی | مدیران صندوق‌های سرمایه‌گذاری | تحلیل‌گران مدیریت | کارمندان صدور اسناد حقوق و ثبت اوقات کار | مشاوران مالی فردی | متخصصان مدیریت پروژه</t>
+          <t>حسابداران و حسابرسان | مدیران خدمات اداری و پشتیبانی | کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران بودجه | مدیران عامل و مدیران ارشد اجرایی | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | تحلیل‌گران اعتبارات و تسهیلات | مسئولان دفاتر و دستیاران اجرایی مدیریت | بازرسان و ارزیابان مالی | مدیران امور مالی | تحلیل‌گران مالی و سرمایه‌گذاری | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران کل و مدیران عملیات | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان تحلیل مدیریت و روش‌ها | کارمندان امور حقوق، دستمزد و ثبت زمان | مشاوران مالی فردی | کارشناسان مدیریت پروژه</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | حقوق و مقررات دولتی | رایانه و الکترونیک | فروش و بازاریابی</t>
+          <t>اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره | قانون و دولت | رایانه و الکترونیک | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال ریاضی | حساسیت به مسئله | وضوح گفتار | بیان کتبی | مهارت محاسبات عددی | دید نزدیک | تشخیص گفتار | درک روابط فضایی | انعطاف‌پذیری در طبقه‌بندی | نوآوری و اصالت | روانی کلام و سیالی ایده‌ها | توجه انتخابی | سرعت ادراک</t>
+          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی | حساسیت به مسئله | وضوح گفتار | بیان کتبی | توانایی عددی | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | اکچوئرها (محاسبان بیمه) | کارمندان کارگزاری | تحلیل‌گران بودجه | تحلیل‌گران هوش تجاری | مدیران ارشد اجرایی | کارشناسان تحلیل شغل، حقوق و مزایا | تحلیل‌گران اعتباری | اقتصاددانان | ممیزان و بازرسان مالی | مدیران امور مالی | تحلیل‌گران کمی مالی | متخصصان مدیریت ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان پرداخت تسهیلات و اعتبارات | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و کارشناسان بازاریابی | مشاوران مالی فردی | کارگزاران و نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | خزانه‌داران و مدیران مالی</t>
+          <t>حسابداران و حسابرسان | اکچوئرها و کارشناسان محاسبات فنی بیمه | کارشناسان امور اداری و معاملات کارگزاری | تحلیل‌گران بودجه | تحلیل‌گران هوش تجاری | مدیران عامل و مدیران ارشد اجرایی | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | تحلیل‌گران اعتبارات و تسهیلات | اقتصاددانان | بازرسان و ارزیابان مالی | مدیران امور مالی | تحلیل‌گران کمّی مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان و مسئولان تسهیلات و اعتبارات | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مشاوران مالی فردی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | استراتژی‌های یادگیری | یادگیری فعال | نگارش | ریاضیات</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | آموزش و تدریس | ریاضیات | امور اداری و منابع انسانی | زبان انگلیسی | مکانیک | مهندسی و فناوری</t>
+          <t>تولید و فرآوری | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | ریاضیات | پرسنل و منابع انسانی | زبان انگلیسی | مکانیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | روانی کلام و سیالی ایده‌ها | بیان کتبی | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | تجسم فضایی | سرعت ادراک | مهارت محاسبات عددی | استدلال ریاضی | نوآوری و اصالت | دید دور | توجه انتخابی | درک روابط فضایی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | بیان کتبی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | تجسم | سرعت ادراکی | توانایی عددی | استدلال ریاضی | اصالت | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران تولید سوخت‌های زیستی | مدیران نیروگاه‌های زیست‌توده | مدیران ساخت‌وساز | سرپرستان رده‌اول کمک‌کاران، کارگران ساده و جابه‌جاکنندگان دستی کالا | سرپرستان رده‌اول مکانیک‌ها، نصاب‌ها و تعمیرکاران | سرپرستان رده‌اول کارگران تولید و بهره‌برداری | مدیران عمومی و عملیاتی | مدیران تولید انرژی زمین‌گرمایی | مدیران نیروگاه‌های برق‌آبی | تکنسین‌ها و کاردان‌های فنی مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک | مهندسان ساخت و تولید | مهندسان مکانیک | کارمندان برنامه‌ریزی، تولید و پیگیری امور | متخصصان مدیریت پروژه | مدیران سیستم‌های کنترل کیفیت | مدیران زنجیره تأمین | مونتاژکاران گروهی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>مدیران تولید سوخت‌های زیستی | مدیران نیروگاه‌های زیست‌توده | مدیران پروژه‌های ساختمانی | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارگران تولید و عملیات | مدیران کل و مدیران عملیات | مدیران تولید انرژی زمین‌گرمایی | مدیران تولید نیروگاه‌های برق‌آبی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک و زنجیره تأمین | مهندسان تولید و ساخت | مهندسان مکانیک | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان مدیریت پروژه | مدیران سیستم‌های کنترل کیفیت | مدیران زنجیره تامین | مونتاژکاران گروهی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | سخن گفتن | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فراوری | آموزش و تدریس | زبان انگلیسی | شیمی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | ریاضیات | مهندسی و فناوری | ایمنی و امنیت عمومی | رایانه و الکترونیک | امور اداری و منابع انسانی</t>
+          <t>تولید و فرآوری | آموزش و پرورش | زبان انگلیسی | شیمی | خدمات مشتری و شخصی | مدیریت و اداره | ریاضیات | مهندسی و فناوری | ایمنی و امنیت عمومی | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | مرتب‌سازی اطلاعات | درک روابط فضایی | دید دور | تشخیص گفتار | روانی کلام و سیالی ایده‌ها | سرعت ادراک | انعطاف‌پذیری در طبقه‌بندی | تمایز دیداری اشکال پنهان | مهارت محاسبات عددی | استدلال ریاضی | نوآوری و اصالت | تمایز رنگ‌ها</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی دور | تشخیص گفتار | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | سرعت بستار | توانایی عددی | استدلال ریاضی | اصالت | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های فنی کالیبراسیون | کاردان‌ها و تکنسین‌های شیمی | شیمیدانان | مدیران انطباق و نظارت بر مقررات | سرپرستان رده‌اول کارگران تولید و بهره‌برداری | تکنسین‌ها و کاردان‌های فنی علوم دامی و صنایع غذایی | دانشمندان و متخصصان صنایع غذایی | مهندسان بهداشت و ایمنی حرفه‌ای، به‌جز مهندسان و بازرسان ایمنی معدن | تکنسین‌ها و کاردان‌های فنی مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | بازرسان، آزمایشگران، درجه‌بندان، نمونه‌برداران و توزین‌گران | مهندسان ساخت و تولید | مهندسان مکانیک | مدیران علوم طبیعی | متخصصان مدیریت پروژه | تحلیل‌گران کنترل کیفیت | مدیران امور رگولاتوری و مقرراتی | کارشناسان آزمون و تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی و صحه‌گذاری فرایند</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌های شیمی | شیمی‌دانان | مدیران تطبیق و نظارت مقرراتی | سرپرستان رده اول کارگران تولید و عملیات | تکنسین‌های علوم و صنایع غذایی | متخصصان و کارشناسان علوم و صنایع غذایی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | مهندسان تولید و ساخت | مهندسان مکانیک | مدیران علوم طبیعی و پایه‌ای | کارشناسان مدیریت پروژه | کارشناسان تحلیل کنترل کیفیت | مدیران امور انطباق مقرراتی و حقوقی صنایع | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | شنیدن فعال | نگارش | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال | نگارش | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | مدیریت و امور اداری | تولید و فراوری | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | زبان انگلیسی | امور اداری و منابع انسانی | آموزش و تدریس | فیزیک | طراحی | شیمی | اداری | حقوق و مقررات دولتی | رایانه و الکترونیک | ساختمان و ساخت‌وساز | اقتصاد و حسابداری</t>
+          <t>مکانیک | مدیریت و اداره | تولید و فرآوری | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | فیزیک | طراحی | شیمی | اداری | قانون و دولت | رایانه و الکترونیک | ساختمان و ساخت‌وساز | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | درک کتبی | بیان کتبی | وضوح گفتار | مرتب‌سازی اطلاعات | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | درک روابط فضایی | مهارت محاسبات عددی | دید دور | روانی کلام و سیالی ایده‌ها | توجه انتخابی | تجسم فضایی | سرعت ادراک</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | درک کتبی | بیان کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی | بینایی دور | روانی ایده‌ها | توجه انتخابی | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنسین‌های فراوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه فناوری و محصولات سوخت زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان انرژی، به‌جز باد و خورشید | اپراتورهای تأسیسات و پالایشگاه گاز | تکنسین‌های انرژی زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مدیران نیروگاه‌های برق‌آبی | مدیران تولید صنعتی | مهندسان نفت | اپراتورهای نیروگاه | مدیران سیستم‌های کنترل کیفیت | اپراتورهای تصفیه‌خانه و شبکه‌های آب و فاضلاب | مهندسان آب و فاضلاب | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | مدیران بهره‌برداری انرژی بادی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری زیست‌سوخت | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان انرژی، به‌جز بادی و خورشیدی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مدیران تولید نیروگاه‌های برق‌آبی | مدیران تولید صنعتی | مهندسان نفت | اپراتورهای نیروگاه برق | مدیران سیستم‌های کنترل کیفیت | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | مهندسان آب و فاضلاب | مدیران توسعه پروژه‌های انرژی بادی | مهندسان انرژی باد | مدیران بهره‌برداری و تعمیرات نیروگاه‌های بادی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نظارت | سخن گفتن | نگارش | استراتژی‌های یادگیری | یادگیری فعال | علوم پایه | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نظارت | سخن گفتن | نگارش | راهبردهای یادگیری | یادگیری فعال | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مدیریت و امور اداری | مکانیک | مهندسی و فناوری | شیمی | ریاضیات | رایانه و الکترونیک | امور اداری و منابع انسانی | فیزیک | اداری | آموزش و تدریس | زبان انگلیسی | طراحی | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری</t>
+          <t>تولید و فرآوری | مدیریت و اداره | مکانیک | مهندسی و فناوری | شیمی | ریاضیات | رایانه و الکترونیک | پرسنل و منابع انسانی | فیزیک | اداری | آموزش و پرورش | زبان انگلیسی | طراحی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | دید نزدیک | توجه انتخابی | استدلال استقرایی | تقسیم توجه | درک روابط فضایی | سرعت ادراک | دید دور | استدلال ریاضی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | نوآوری و اصالت | روانی کلام و سیالی ایده‌ها | تمایز رنگ‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | بینایی نزدیک | توجه انتخابی | استدلال استقرایی | تقسیم توجه | انعطاف‌پذیری بستار | سرعت ادراکی | بینایی دور | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های فراوری سوخت‌های زیستی | مدیران توسعه فناوری و محصولات سوخت زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | اپراتورهای فرایند و کارخانه‌های شیمیایی | مهندسان انرژی، به‌جز باد و خورشید | اپراتورهای تأسیسات و پالایشگاه گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مدیران نیروگاه‌های برق‌آبی | مهندسان صنایع | مدیران تولید صنعتی | مهندسان ساخت و تولید | اپراتورها و متصدیان اندازه‌گیری و پمپاژ در پالایشگاه نفت | اپراتورهای نیروگاه | مدیران سیستم‌های کنترل کیفیت | اپراتورهای تصفیه‌خانه و شبکه‌های آب و فاضلاب | مدیران توسعه انرژی بادی | مدیران بهره‌برداری انرژی بادی</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | مدیران توسعه محصول و فناوری زیست‌سوخت | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | مهندسان انرژی، به‌جز بادی و خورشیدی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مدیران تولید نیروگاه‌های برق‌آبی | مهندسان صنایع | مدیران تولید صنعتی | مهندسان تولید و ساخت | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | مدیران سیستم‌های کنترل کیفیت | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | مدیران توسعه پروژه‌های انرژی بادی | مدیران بهره‌برداری و تعمیرات نیروگاه‌های بادی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
